--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_390_Japan_main_islands.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_390_Japan_main_islands.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R97059016da5642d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rb699a321ef9d4f82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rad79a6b10a1d4411"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rfc588dd538c74671"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R6d46f2542c7a4bf8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Re471360ef56e4a0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc7fed8e2b94843de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R6b11b61d446f4449"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rfc34dee8eb944885"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R34a6f5a6a67e4e06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R602e4cde30dc4c67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rf9f8b30656604e90"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ390CommercialTable" displayName="EEZ390CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ390CommercialTable" displayName="EEZ390CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ390FunctionalTable" displayName="EEZ390FunctionalTable" ref="A1:O24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O24"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ390FunctionalTable" displayName="EEZ390FunctionalTable" ref="A1:E24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E24"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ390ValidationTable" displayName="EEZ390ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ390ValidationTable" displayName="EEZ390ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -12620,7 +12574,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62792778b3f14b70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb573ef0c6a54b52"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12630,20 +12584,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -12651,714 +12595,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>469134.1211878016</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.14</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>138.03842646028852</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>469134.1211878016</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>138.03842646028852</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$179,A2,'Species'!$U$2:$U$179))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>64758535.88759443</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.14</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>138.03842646028852</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>64758535.88759443</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>268529.2111642366</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.6915771211791477</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>491.56066284675916</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>268529.2111642366</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>612.3451779027205</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$179,A3,'Species'!$U$2:$U$179))</x:f>
-        <x:v>164432567.58244166</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.6915771211791477</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>491.56066284675916</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>131998397.0336095</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>32434170.548832163</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.2457163971512</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.24571639715119994</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>310491.54408939014</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.013177257030693</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>103.08067577504309</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>310491.54408939014</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>223.2110055693268</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$179,A4,'Species'!$U$2:$U$179))</x:f>
-        <x:v>69305129.77696574</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.013177257030693</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>103.08067577504309</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>32005678.187170923</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>37299451.589794815</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>2.165401069512279</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>1.1654010695122792</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>68398.35405006939</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.5807514291822846</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>380.84778069427057</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>68398.35405006939</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>482.63701800720486</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$179,A5,'Species'!$U$2:$U$179))</x:f>
-        <x:v>33011577.635326516</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.5807514291822846</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>380.84778069427057</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>26049361.343109902</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>6962216.292216614</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2672701338245336</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.2672701338245335</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1184912.674579494</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.9026794037198296</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>79.92440350645934</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1184912.674579494</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>89.19428690458882</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$179,A6,'Species'!$U$2:$U$179))</x:f>
-        <x:v>105687441.05332707</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.9026794037198296</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>79.92440350645934</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>94703438.72300942</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>10984002.330317646</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1159831414616725</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.11598314146167261</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>499369.0852357467</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0297848228244257</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.709885377560008</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>499369.0852357467</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>11.377183892838211</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$179,A7,'Species'!$U$2:$U$179))</x:f>
-        <x:v>5681413.913125489</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0297848228244257</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.709885377560008</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>5348185.66397184</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>333228.2491536485</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.062306784036771</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.06230678403677106</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1154493.2716378225</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4973975877569052</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>314.3385082088168</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1154493.2716378225</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>492.4817164964909</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$179,A8,'Species'!$U$2:$U$179))</x:f>
-        <x:v>568566828.0998443</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4973975877569052</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>314.3385082088168</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>362901692.74374944</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>205665135.3560949</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.5667241004062173</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5667241004062173</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1570282.509519579</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.674474646276029</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>472.57924733863626</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1570282.509519579</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>784.4715121731101</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$179,A9,'Species'!$U$2:$U$179))</x:f>
-        <x:v>1231841894.7818103</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.674474646276029</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>472.57924733863626</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>742082926.4577875</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>489758968.32402277</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.6599787582525416</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.6599787582525416</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>122886.46255197491</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9220529296303055</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>835.704863536548</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>122886.46255197491</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>864.4138835018834</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$179,A10,'Species'!$U$2:$U$179))</x:f>
-        <x:v>106224764.3243614</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9220529296303055</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>835.704863536548</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>102696814.41748731</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>3527949.9068740904</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0343530607729674</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.03435306077296734</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>53410.2164317602</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.619423353793733</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>416.3162412143033</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>53410.2164317602</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>419.97659609142994</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$179,A11,'Species'!$U$2:$U$179))</x:f>
-        <x:v>22431040.893517207</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.619423353793733</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>416.3162412143033</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>22235540.547312826</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>195500.34620438144</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.008792246169523</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.00879224616952286</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>26015.9842324185</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.011302129442597</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1026.3656987514862</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>26015.9842324185</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1045.8681511005798</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$179,A12,'Species'!$U$2:$U$179))</x:f>
-        <x:v>27209289.328221373</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.011302129442597</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1026.3656987514862</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>26701913.835413862</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>507375.49280751124</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0190014654355821</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.01900146543558222</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>234366.8938147432</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.4008111532341445</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2516.5823898183135</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>234366.8938147432</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2551.4550299683565</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$179,A13,'Species'!$U$2:$U$179))</x:f>
-        <x:v>597976590.0816863</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.4008111532341445</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2516.5823898183135</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>589803597.7306013</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>8172992.351084948</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0138571422462195</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.013857142246219468</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b457ade354542fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ec33a99863d4361"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13368,20 +12848,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13389,1308 +12859,459 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>190729.24517054527</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.017919457171402</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1042.1241425490477</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>190729.24517054527</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1219.009202716236</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$179,A2,'Species'!$U$2:$U$179))</x:f>
-        <x:v>232500705.09001586</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.017919457171402</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1042.1241425490477</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>198763551.0823816</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>33737154.00763425</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1697351140282817</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.16973511402828179</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>479</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.010939457202505</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>102.55089552687535</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>479</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>102.71776238274046</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$179,A3,'Species'!$U$2:$U$179))</x:f>
-        <x:v>49201.80818133268</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.010939457202505</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>102.55089552687535</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>49121.878957373294</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>79.92922395938513</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0016271613719978</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0016271613719977132</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>373933.6089228747</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.171622672153647</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1484.645178282005</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>373933.6089228747</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1900.2892952967154</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$179,A4,'Species'!$U$2:$U$179))</x:f>
-        <x:v>710582034.1878071</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.171622672153647</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1484.645178282005</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>555158729.4849348</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>155423304.70287228</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2799619216058638</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.2799619216058638</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>126526.4828982717</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.146056300175386</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1399.7687711580716</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>126526.4828982717</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1567.4795453765573</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$179,A5,'Species'!$U$2:$U$179))</x:f>
-        <x:v>198327673.89147767</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.146056300175386</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1399.7687711580716</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>177107819.48546654</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>21219854.406011134</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1198131989183708</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.11981319891837093</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>8024.0388894554</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.25</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1778.2794100389228</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>8024.0388894554</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1778.2794100389228</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$179,A6,'Species'!$U$2:$U$179))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>14268983.142470121</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.25</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1778.2794100389228</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>14268983.142470121</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>306190.6585080216</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.391973617047501</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2465.8895323778693</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>306190.6585080216</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2496.3873237737102</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$179,A7,'Species'!$U$2:$U$179))</x:f>
-        <x:v>764370478.5573502</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.391973617047501</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2465.8895323778693</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>755032339.7268173</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>9338138.830532908</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0123678660359259</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.01236786603592582</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>642.0219096521</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.7200077884182035</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>524.816871966472</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>642.0219096521</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>524.8183006576966</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$179,A8,'Species'!$U$2:$U$179))</x:f>
-        <x:v>336944.8476086243</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.7200077884182035</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>524.816871966472</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>336943.93035755603</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0.9172510682838038</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0000027222661863</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.000002722266186277465</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>8493.652569728101</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6045804357544573</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>402.328164365995</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>8493.652569728101</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>439.6298289897229</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$179,A9,'Species'!$U$2:$U$179))</x:f>
-        <x:v>3734063.0267276857</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6045804357544573</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>402.328164365995</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3417235.6471412233</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>316827.3795864624</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.09271452492646</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.09271452492645993</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>25373.9623227664</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.0186725726834425</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1043.932870920709</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>25373.9623227664</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1059.0519580184741</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$179,A10,'Species'!$U$2:$U$179))</x:f>
-        <x:v>26872344.480612747</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.0186725726834425</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1043.932870920709</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>26488713.334239434</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>383631.1463733129</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0144828154366194</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.014482815436619547</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>152549.6662871621</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.4168239674339627</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>261.1102781685655</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>152549.6662871621</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>371.8023793831053</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$179,A11,'Species'!$U$2:$U$179))</x:f>
-        <x:v>56718328.89966555</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.4168239674339627</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>261.1102781685655</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>39832285.79876274</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>16886043.10090281</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.4239285484697772</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.4239285484697773</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>112.0000000002</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.98</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>954.992586021436</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>112.0000000002</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>954.992586021436</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$179,A12,'Species'!$U$2:$U$179))</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>106959.16963459183</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.98</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>954.992586021436</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
-        <x:v>106959.16963459183</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>332664.3096459172</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.5374833913829895</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>344.7334227655955</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>332664.3096459172</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>357.3187569211121</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$179,A13,'Species'!$U$2:$U$179))</x:f>
-        <x:v>118867197.59469905</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.5374833913829895</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>344.7334227655955</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>114680506.09619094</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>4186691.4985081106</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0365074382824613</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.03650743828246124</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>993084.443148333</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.3246337107731447</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>211.17072490763164</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>993084.443148333</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>231.4212101183857</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$179,A14,'Species'!$U$2:$U$179))</x:f>
-        <x:v>229820803.58313042</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.3246337107731447</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>211.17072490763164</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>209710361.75412518</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>20110441.82900524</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0958962716996488</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.09589627169964887</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1917771.1280703933</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.202915454632573</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>159.55685030487348</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1917771.1280703933</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>241.38473418368417</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$179,A15,'Species'!$U$2:$U$179))</x:f>
-        <x:v>462920673.974416</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.202915454632573</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>159.55685030487348</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>305993520.8005361</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>156927153.17387992</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.5128446928004529</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.5128446928004529</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>44722.101590656</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.3687280922589626</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>233.7373372693523</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>44722.101590656</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>314.479470609261</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$179,A16,'Species'!$U$2:$U$179))</x:f>
-        <x:v>14064182.832763087</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.3687280922589626</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>233.7373372693523</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>10453224.942889398</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>3610957.889873689</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.3454396044858838</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.3454396044858838</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>519225.65192316263</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.043493238226791</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>11.053332596983601</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>519225.65192316263</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>11.920501299662089</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$179,A17,'Species'!$U$2:$U$179))</x:f>
-        <x:v>6189430.058567955</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.043493238226791</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>11.053332596983601</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>5739173.823592355</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>450256.2349756006</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0784531447931942</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.07845314479319414</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>157941.87780222812</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.623311239057712</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>42.00599139384797</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>157941.87780222812</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>79.69261257651456</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$179,A18,'Species'!$U$2:$U$179))</x:f>
-        <x:v>12586800.877300171</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.623311239057712</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>42.00599139384797</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>6634505.159688583</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>5952295.717611589</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.8971725206844188</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.8971725206844189</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small bathydemersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>7122.0483468063</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.51</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>323.5936569296281</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>7122.0483468063</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$179,A19,'Species'!$U$2:$U$179))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>2304649.669372663</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.51</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>2304649.669372663</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small bathypelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>2563.5708792354</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.1</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>125.89254117941675</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>2563.5708792354</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>125.89254117941675</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$179,A20,'Species'!$U$2:$U$179))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>322734.4524804962</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.1</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>125.89254117941675</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>322734.4524804962</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>1697.5763304790999</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.990979669423084</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>979.4441337315133</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>1697.5763304790999</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>986.1578133404774</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$179,A21,'Species'!$U$2:$U$179))</x:f>
-        <x:v>1674078.1620438208</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.990979669423084</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>979.4441337315133</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>1662681.178449223</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>11396.983594597783</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0068545814689667</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.006854581468966715</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>102292.2404939109</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.2390897267819416</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>173.41622448223</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>102292.2404939109</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>241.51657668776338</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$179,A22,'Species'!$U$2:$U$179))</x:f>
-        <x:v>24705271.745810766</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.2390897267819416</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>173.41622448223</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>17739134.14028231</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>6966137.605528455</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.3926988516147267</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.3926988516147267</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>629776.7276248229</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.175769641281077</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>149.88895827715916</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>629776.7276248229</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>154.1196023220659</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$179,A23,'Species'!$U$2:$U$179))</x:f>
-        <x:v>97060938.81322972</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.175769641281077</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>149.88895827715916</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>94396577.6508829</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>2664361.162346825</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0282251881228228</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.02822518812282285</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>60374.315160614</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.491805052818962</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>310.31663184734833</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>60374.315160614</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>310.43986905682334</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$179,A24,'Species'!$U$2:$U$179))</x:f>
-        <x:v>18742594.492856394</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.491805052818962</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>310.31663184734833</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>18735154.130732037</x:v>
       </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>7440.3621243573725</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0003971337557427</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.00039713375574277466</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G24">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O24">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R531af140bec14edd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R084787c5732f464c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14865,7 +13486,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -14964,7 +13585,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>2997127073.358222</x:v>
+        <x:v>2201286082.570818</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -14978,7 +13599,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>2997127073.3582225</x:v>
+        <x:v>2558934906.4803843</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -14992,7 +13613,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>4.76837158203125e-7</x:v>
+        <x:v>-795840990.7874036</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15006,7 +13627,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>9.5367431640625e-7</x:v>
+        <x:v>-438192166.8778372</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15017,9 +13638,9 @@
         <x:v>EEZ_390</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -15031,47 +13652,19 @@
         <x:v>EEZ_390</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_390</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_390</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9040dc3b5a743ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ed7ecb929c84bca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15118,7 +13711,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
